--- a/trading_signals/risk_management/risk_workbook_20260610_031024.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260610_031024.xlsx
@@ -731,7 +731,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-09  ·  Generated 2026-06-10T10:04:12  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-09  ·  Generated 2026-06-24T18:50:51  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1055626.23</v>
+        <v>1055689.39</v>
       </c>
     </row>
     <row r="5">
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1.124</v>
+        <v>1.123</v>
       </c>
     </row>
     <row r="12">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.8037</v>
+        <v>0.8035</v>
       </c>
     </row>
     <row r="13">
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>8.85</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -843,7 +843,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>4.0 / 2.0</t>
+          <t>3.99 / 1.99</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>STLD (25.92% NAV)</t>
+          <t>STLD (25.91% NAV)</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
         <v>3796</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>33957776</v>
+        <v>33957786</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
@@ -1280,11 +1280,11 @@
           <t>KLAC/REGN</t>
         </is>
       </c>
-      <c r="C9" s="15" t="n">
-        <v>67</v>
+      <c r="C9" s="13" t="n">
+        <v>670</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>1035211</v>
+        <v>2296336</v>
       </c>
       <c r="E9" s="17" t="n">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>23</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1100317</v>
+        <v>1100320</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>0</v>
@@ -1410,7 +1410,7 @@
         <v>2359</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>3806048</v>
+        <v>3806061</v>
       </c>
       <c r="E15" s="17" t="n">
         <v>0</v>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="B4" s="19" t="n">
-        <v>-30402.04</v>
+        <v>-30403.85</v>
       </c>
       <c r="C4" s="22" t="n">
         <v>-2.88</v>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="B5" s="18" t="n">
-        <v>-60804.07</v>
+        <v>-60807.71</v>
       </c>
       <c r="C5" s="20" t="n">
         <v>-5.76</v>
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>-30402.04</v>
+        <v>-30403.85</v>
       </c>
       <c r="C6" s="22" t="n">
         <v>-2.88</v>
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="C6" s="30" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="D6" s="30" t="n">
         <v>3</v>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="D7" s="32" t="n">
         <v>0.5</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>25.92</v>
+        <v>25.91</v>
       </c>
       <c r="D8" s="32" t="n">
         <v>15</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="E6" s="25" t="n">
-        <v>67</v>
+        <v>670</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>2139.37</v>
+        <v>213.94</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>143337.79</v>
@@ -3439,16 +3439,16 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>14.75</v>
+        <v>15.07</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>0.09</v>
+        <v>0.35</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>25</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>-14.66</v>
+        <v>-14.72</v>
       </c>
     </row>
     <row r="7">
@@ -3458,16 +3458,16 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>12.65</v>
+        <v>12.98</v>
       </c>
       <c r="C7" s="17" t="n">
-        <v>19.23</v>
+        <v>23.32</v>
       </c>
       <c r="D7" s="17" t="n">
         <v>25</v>
       </c>
       <c r="E7" s="21" t="n">
-        <v>6.57</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="8">
@@ -3477,16 +3477,16 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>25.08</v>
+        <v>25.66</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>3.21</v>
+        <v>3.66</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>25</v>
       </c>
       <c r="E8" s="22" t="n">
-        <v>-21.87</v>
+        <v>-21.99</v>
       </c>
     </row>
     <row r="9">
@@ -3496,16 +3496,16 @@
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>47.52</v>
+        <v>46.29</v>
       </c>
       <c r="C9" s="17" t="n">
-        <v>77.47</v>
+        <v>72.67</v>
       </c>
       <c r="D9" s="17" t="n">
         <v>25</v>
       </c>
       <c r="E9" s="21" t="n">
-        <v>29.95</v>
+        <v>26.38</v>
       </c>
     </row>
     <row r="11">
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="B5" s="27" t="n">
-        <v>38.97</v>
+        <v>38.94</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>2.6</v>
@@ -3758,7 +3758,7 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>-0.111 (t=-0.62)</t>
+          <t>-0.11 (t=-0.62)</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>48.07</v>
+        <v>47.74</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="D6" s="17" t="n">
         <v>0.059</v>
@@ -3787,27 +3787,27 @@
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>0.056 (t=0.39)</t>
+          <t>0.059 (t=0.41)</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
         <is>
-          <t>-0.116 (t=-0.52)</t>
+          <t>-0.119 (t=-0.54)</t>
         </is>
       </c>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t>-0.06 (t=-0.31)</t>
+          <t>-0.059 (t=-0.3)</t>
         </is>
       </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
-          <t>0.241 (t=1.31)</t>
+          <t>0.244 (t=1.32)</t>
         </is>
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t>-0.207 (t=-0.72)</t>
+          <t>-0.208 (t=-0.72)</t>
         </is>
       </c>
       <c r="K6" s="17" t="inlineStr">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>28.62</v>
+        <v>29.07</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>1.03</v>
@@ -3836,32 +3836,32 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>-0.069 (t=-0.42)</t>
+          <t>-0.073 (t=-0.44)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>-0.004 (t=-0.02)</t>
+          <t>0.001 (t=0.0)</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>0.235 (t=1.04)</t>
+          <t>0.234 (t=1.03)</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>-0.103 (t=-0.49)</t>
+          <t>-0.106 (t=-0.5)</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>0.022 (t=0.07)</t>
+          <t>0.023 (t=0.07)</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>-0.065 (t=-0.55)</t>
+          <t>-0.064 (t=-0.53)</t>
         </is>
       </c>
     </row>
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>0.171</v>
+        <v>0.174</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>25.133</v>
+        <v>25.183</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>0</v>
@@ -3962,10 +3962,10 @@
         <v>1</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>2.239</v>
+        <v>2.243</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>2.239</v>
+        <v>2.243</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>0</v>
@@ -3978,10 +3978,10 @@
         </is>
       </c>
       <c r="B5" s="17" t="n">
-        <v>-0.381</v>
+        <v>-0.419</v>
       </c>
       <c r="C5" s="17" t="n">
-        <v>2.339</v>
+        <v>2.471</v>
       </c>
       <c r="D5" s="17" t="n">
         <v>0</v>
@@ -3990,13 +3990,13 @@
         <v>1</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>1.594</v>
+        <v>1.602</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>1.654</v>
+        <v>1.67</v>
       </c>
       <c r="H5" s="17" t="n">
-        <v>0.06</v>
+        <v>0.067</v>
       </c>
     </row>
     <row r="6">
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1.622</v>
+        <v>1.624</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>29.868</v>
+        <v>29.722</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>0</v>
@@ -4018,10 +4018,10 @@
         <v>1</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>4.812</v>
+        <v>4.818</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>4.812</v>
+        <v>4.818</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>0</v>
@@ -4086,16 +4086,16 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.124</v>
+        <v>1.123</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>0.8037</v>
+        <v>0.8035</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>8.85</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="F9" s="7" t="n">
         <v>9.470000000000001</v>
@@ -4104,10 +4104,10 @@
         <v>76.2</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="J9" s="7" t="n">
         <v>1.425</v>
@@ -4120,13 +4120,13 @@
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>1.219</v>
+        <v>1.195</v>
       </c>
       <c r="C10" s="17" t="n">
-        <v>0.8214</v>
+        <v>0.8165</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>477</v>
+        <v>496</v>
       </c>
       <c r="E10" s="17" t="n">
         <v>9.02</v>
@@ -4138,10 +4138,10 @@
         <v>76.8</v>
       </c>
       <c r="H10" s="17" t="n">
-        <v>5.63</v>
+        <v>5.47</v>
       </c>
       <c r="I10" s="17" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="J10" s="17" t="n">
         <v>0.343</v>
@@ -4154,13 +4154,13 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>0.822</v>
+        <v>0.829</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>0.743</v>
+        <v>0.7449</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>948</v>
+        <v>931</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>15.56</v>
@@ -4172,13 +4172,13 @@
         <v>79.5</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="I11" s="7" t="n">
         <v>0.75</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>2.686</v>
+        <v>2.68</v>
       </c>
     </row>
   </sheetData>
@@ -4253,16 +4253,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>38690.57</v>
+        <v>38753.73</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>239750.22</v>
+        <v>239825.86</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>617546.34</v>
+        <v>617429.26</v>
       </c>
     </row>
     <row r="6">
@@ -4310,16 +4310,16 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>1552812.37</v>
+        <v>1552875.53</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>1395328.77</v>
+        <v>1395404.41</v>
       </c>
       <c r="D8" s="13" t="n">
         <v>3675223.35</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>1463317.41</v>
+        <v>1463200.33</v>
       </c>
     </row>
     <row r="9">
@@ -4354,7 +4354,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>1252184.45</v>
+        <v>1252060.75</v>
       </c>
       <c r="E10" s="15" t="n">
         <v>0</v>
@@ -4373,7 +4373,7 @@
         <v>331603.61</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2575565.99</v>
+        <v>2575442.29</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>444005.67</v>
@@ -4386,16 +4386,16 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>1055626.23</v>
+        <v>1055689.39</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>1063725.16</v>
+        <v>1063800.8</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1099657.36</v>
+        <v>1099781.06</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>1019311.74</v>
+        <v>1019194.66</v>
       </c>
     </row>
     <row r="13">
@@ -4462,16 +4462,16 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>754790.61</v>
+        <v>754853.77</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>833935.86</v>
+        <v>834011.5</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>369906.22</v>
+        <v>370029.92</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>851933.55</v>
+        <v>851816.47</v>
       </c>
     </row>
     <row r="17">
@@ -4490,7 +4490,7 @@
         <v>-0</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="19">
@@ -4540,7 +4540,7 @@
         <v>817342.87</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1099657.36</v>
+        <v>1099781.06</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>392885.28</v>
@@ -4597,7 +4597,7 @@
         <v>0</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>1225716.82</v>
+        <v>1225593.12</v>
       </c>
       <c r="E24" s="15" t="n">
         <v>0</v>
@@ -4616,7 +4616,7 @@
         <v>817342.87</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1099657.36</v>
+        <v>1099781.06</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>392885.28</v>
@@ -4743,16 +4743,16 @@
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>38690.57</v>
+        <v>38753.73</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>239750.22</v>
+        <v>239825.86</v>
       </c>
       <c r="D32" s="15" t="n">
         <v>0</v>
       </c>
       <c r="E32" s="13" t="n">
-        <v>617546.34</v>
+        <v>617429.26</v>
       </c>
     </row>
     <row r="33">
@@ -4762,16 +4762,16 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>1055626.23</v>
+        <v>1055689.39</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1063725.16</v>
+        <v>1063800.8</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1099657.36</v>
+        <v>1099781.06</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1019311.74</v>
+        <v>1019194.66</v>
       </c>
     </row>
     <row r="34">
@@ -4834,16 +4834,16 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>469129.15</v>
+        <v>468101.76</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>569544.12</v>
+        <v>568514.2</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>478778.84</v>
+        <v>477734.47</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>444798.09</v>
+        <v>443726.45</v>
       </c>
     </row>
     <row r="40">
@@ -4891,16 +4891,16 @@
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>665705.01</v>
+        <v>664677.62</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>569544.12</v>
+        <v>568514.2</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>662587.01</v>
+        <v>661542.64</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>754998.17</v>
+        <v>753926.53</v>
       </c>
     </row>
     <row r="43">
@@ -4967,16 +4967,16 @@
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>568147.8100000001</v>
+        <v>567120.42</v>
       </c>
       <c r="C46" s="13" t="n">
-        <v>569544.12</v>
+        <v>568514.2</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>577532.67</v>
+        <v>576488.3</v>
       </c>
       <c r="E46" s="13" t="n">
-        <v>592620.54</v>
+        <v>591548.9</v>
       </c>
     </row>
     <row r="47">
@@ -4992,10 +4992,10 @@
         <v>0</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>0.315</v>
+        <v>0.316</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>0.518</v>
+        <v>0.519</v>
       </c>
     </row>
     <row r="48">
@@ -5043,16 +5043,16 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>529222.87</v>
+        <v>528195.48</v>
       </c>
       <c r="C50" s="13" t="n">
-        <v>569544.12</v>
+        <v>568514.2</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>541111.25</v>
+        <v>540066.88</v>
       </c>
       <c r="E50" s="13" t="n">
-        <v>531230.03</v>
+        <v>530158.39</v>
       </c>
     </row>
     <row r="51">
@@ -5324,16 +5324,16 @@
         </is>
       </c>
       <c r="B66" s="13" t="n">
-        <v>469129.15</v>
+        <v>468101.76</v>
       </c>
       <c r="C66" s="13" t="n">
-        <v>569544.12</v>
+        <v>568514.2</v>
       </c>
       <c r="D66" s="13" t="n">
-        <v>478778.84</v>
+        <v>477734.47</v>
       </c>
       <c r="E66" s="13" t="n">
-        <v>444798.09</v>
+        <v>443726.45</v>
       </c>
     </row>
     <row r="67">
@@ -5343,16 +5343,16 @@
         </is>
       </c>
       <c r="B67" s="4" t="n">
-        <v>568147.8100000001</v>
+        <v>567120.42</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>569544.12</v>
+        <v>568514.2</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>577532.67</v>
+        <v>576488.3</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>592620.54</v>
+        <v>591548.9</v>
       </c>
     </row>
     <row r="68">
@@ -5424,7 +5424,7 @@
         <v>0</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>172748.26</v>
+        <v>173702.83</v>
       </c>
     </row>
     <row r="74">
@@ -5481,7 +5481,7 @@
         <v>3491415.19</v>
       </c>
       <c r="E76" s="13" t="n">
-        <v>708319.24</v>
+        <v>709273.8100000001</v>
       </c>
     </row>
     <row r="77">
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="B78" s="13" t="n">
-        <v>430438.58</v>
+        <v>429348.03</v>
       </c>
       <c r="C78" s="13" t="n">
-        <v>329793.89</v>
+        <v>328688.34</v>
       </c>
       <c r="D78" s="13" t="n">
-        <v>1730963.3</v>
+        <v>1729795.24</v>
       </c>
       <c r="E78" s="15" t="n">
         <v>0</v>
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>830067.52</v>
+        <v>828976.97</v>
       </c>
       <c r="C79" s="4" t="n">
-        <v>661397.5</v>
+        <v>660291.95</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>2969290.5</v>
+        <v>2968122.44</v>
       </c>
       <c r="E79" s="4" t="n">
         <v>281628.04</v>
@@ -5548,16 +5548,16 @@
         </is>
       </c>
       <c r="B80" s="13" t="n">
-        <v>487478.42</v>
+        <v>488568.97</v>
       </c>
       <c r="C80" s="13" t="n">
-        <v>494181.05</v>
+        <v>495286.6</v>
       </c>
       <c r="D80" s="13" t="n">
-        <v>522124.69</v>
+        <v>523292.75</v>
       </c>
       <c r="E80" s="13" t="n">
-        <v>426691.2</v>
+        <v>427645.77</v>
       </c>
     </row>
     <row r="81">
@@ -5567,16 +5567,16 @@
         </is>
       </c>
       <c r="B81" s="7" t="n">
-        <v>2.686</v>
+        <v>2.68</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>2.325</v>
+        <v>2.32</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>6.64</v>
+        <v>6.625</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>1.242</v>
+        <v>1.239</v>
       </c>
     </row>
     <row r="82">
@@ -5586,13 +5586,13 @@
         </is>
       </c>
       <c r="B82" s="17" t="n">
-        <v>1.047</v>
+        <v>1.044</v>
       </c>
       <c r="C82" s="17" t="n">
-        <v>0.983</v>
+        <v>0.981</v>
       </c>
       <c r="D82" s="17" t="n">
-        <v>1.896</v>
+        <v>1.892</v>
       </c>
       <c r="E82" s="17" t="n">
         <v>-0.078</v>
@@ -5624,16 +5624,16 @@
         </is>
       </c>
       <c r="B84" s="13" t="n">
-        <v>225567.75</v>
+        <v>226658.3</v>
       </c>
       <c r="C84" s="13" t="n">
-        <v>264391.75</v>
+        <v>265497.3</v>
       </c>
       <c r="D84" s="18" t="n">
-        <v>-171205.04</v>
+        <v>-170036.98</v>
       </c>
       <c r="E84" s="13" t="n">
-        <v>320703.51</v>
+        <v>321658.08</v>
       </c>
     </row>
     <row r="85">
@@ -5643,13 +5643,13 @@
         </is>
       </c>
       <c r="B85" s="7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C85" s="7" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E85" s="7" t="n">
         <v>0</v>
@@ -5696,13 +5696,13 @@
         </is>
       </c>
       <c r="B89" s="4" t="n">
-        <v>487478.42</v>
+        <v>488568.97</v>
       </c>
       <c r="C89" s="4" t="n">
-        <v>494181.05</v>
+        <v>495286.6</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>522124.69</v>
+        <v>523292.75</v>
       </c>
       <c r="E89" s="4" t="n">
         <v>248310.38</v>
@@ -5753,13 +5753,13 @@
         </is>
       </c>
       <c r="B92" s="13" t="n">
-        <v>422446</v>
+        <v>421355.45</v>
       </c>
       <c r="C92" s="13" t="n">
-        <v>323161.82</v>
+        <v>322056.27</v>
       </c>
       <c r="D92" s="13" t="n">
-        <v>1706196.75</v>
+        <v>1705028.69</v>
       </c>
       <c r="E92" s="15" t="n">
         <v>0</v>
@@ -5772,13 +5772,13 @@
         </is>
       </c>
       <c r="B93" s="4" t="n">
-        <v>487478.42</v>
+        <v>488568.97</v>
       </c>
       <c r="C93" s="4" t="n">
-        <v>494181.05</v>
+        <v>495286.6</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>522124.69</v>
+        <v>523292.75</v>
       </c>
       <c r="E93" s="4" t="n">
         <v>248310.38</v>
@@ -5914,7 +5914,7 @@
         <v>0</v>
       </c>
       <c r="E100" s="13" t="n">
-        <v>172748.26</v>
+        <v>173702.83</v>
       </c>
     </row>
     <row r="101">
@@ -5924,16 +5924,16 @@
         </is>
       </c>
       <c r="B101" s="4" t="n">
-        <v>487478.42</v>
+        <v>488568.97</v>
       </c>
       <c r="C101" s="4" t="n">
-        <v>494181.05</v>
+        <v>495286.6</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>522124.69</v>
+        <v>523292.75</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>426691.2</v>
+        <v>427645.77</v>
       </c>
     </row>
     <row r="102">
@@ -6027,16 +6027,16 @@
         </is>
       </c>
       <c r="B5" s="19" t="n">
-        <v>-8098.93</v>
+        <v>-8111.41</v>
       </c>
       <c r="C5" s="19" t="n">
-        <v>-44031.13</v>
+        <v>-44091.67</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>36314.49</v>
+        <v>36494.73</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>134127.44</v>
+        <v>134190.6</v>
       </c>
     </row>
     <row r="6">
@@ -6109,16 +6109,16 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>-1396.31</v>
+        <v>-1393.78</v>
       </c>
       <c r="C11" s="19" t="n">
-        <v>-9384.860000000001</v>
+        <v>-9367.879999999999</v>
       </c>
       <c r="D11" s="19" t="n">
-        <v>-24472.73</v>
+        <v>-24428.48</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>58815.87</v>
+        <v>57788.48</v>
       </c>
     </row>
     <row r="12">
@@ -6191,16 +6191,16 @@
         </is>
       </c>
       <c r="B17" s="19" t="n">
-        <v>-6702.63</v>
+        <v>-6717.63</v>
       </c>
       <c r="C17" s="19" t="n">
-        <v>-34646.27</v>
+        <v>-34723.78</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>60787.22</v>
+        <v>60923.2</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>75311.57000000001</v>
+        <v>76402.12</v>
       </c>
     </row>
     <row r="18">
@@ -6210,16 +6210,16 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>58.96</v>
+        <v>58.81</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>294.82</v>
+        <v>294.07</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>1238.25</v>
+        <v>1235.11</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>8903.59</v>
+        <v>8881.030000000001</v>
       </c>
     </row>
     <row r="19">
@@ -6311,13 +6311,13 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1063725.16</v>
+        <v>1063800.8</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1099657.36</v>
+        <v>1099781.06</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1019311.74</v>
+        <v>1019194.66</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>921498.79</v>
@@ -6330,16 +6330,16 @@
         </is>
       </c>
       <c r="B6" s="18" t="n">
-        <v>-8098.93</v>
+        <v>-8111.41</v>
       </c>
       <c r="C6" s="18" t="n">
-        <v>-44031.13</v>
+        <v>-44091.67</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>36314.49</v>
+        <v>36494.73</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>134127.44</v>
+        <v>134190.6</v>
       </c>
     </row>
     <row r="7">
@@ -6387,16 +6387,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1055626.23</v>
+        <v>1055689.39</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1055626.23</v>
+        <v>1055689.39</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1055626.23</v>
+        <v>1055689.39</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1055626.23</v>
+        <v>1055689.39</v>
       </c>
     </row>
     <row r="10">
@@ -6409,10 +6409,10 @@
         <v>-0.76</v>
       </c>
       <c r="C10" s="20" t="n">
-        <v>-4</v>
+        <v>-4.01</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="E10" s="21" t="n">
         <v>14.56</v>
@@ -6428,10 +6428,10 @@
         <v>-0.76</v>
       </c>
       <c r="C11" s="22" t="n">
-        <v>-9.4</v>
+        <v>-9.41</v>
       </c>
       <c r="D11" s="22" t="n">
-        <v>-9.4</v>
+        <v>-9.41</v>
       </c>
       <c r="E11" s="22" t="n">
         <v>-9.470000000000001</v>
@@ -6478,13 +6478,13 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>569544.12</v>
+        <v>568514.2</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>577532.67</v>
+        <v>576488.3</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>592620.54</v>
+        <v>591548.9</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>509331.94</v>
@@ -6497,16 +6497,16 @@
         </is>
       </c>
       <c r="B16" s="18" t="n">
-        <v>-1396.31</v>
+        <v>-1393.78</v>
       </c>
       <c r="C16" s="18" t="n">
-        <v>-9384.860000000001</v>
+        <v>-9367.879999999999</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>-24472.73</v>
+        <v>-24428.48</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>58815.87</v>
+        <v>57788.48</v>
       </c>
     </row>
     <row r="17">
@@ -6554,16 +6554,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>568147.8100000001</v>
+        <v>567120.42</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>568147.8100000001</v>
+        <v>567120.42</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>568147.8100000001</v>
+        <v>567120.42</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>568147.8100000001</v>
+        <v>567120.42</v>
       </c>
     </row>
     <row r="20">
@@ -6582,7 +6582,7 @@
         <v>-4.13</v>
       </c>
       <c r="E20" s="21" t="n">
-        <v>11.55</v>
+        <v>11.35</v>
       </c>
     </row>
     <row r="21">
@@ -6645,13 +6645,13 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>494181.05</v>
+        <v>495286.6</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>522124.69</v>
+        <v>523292.75</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>426691.2</v>
+        <v>427645.77</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>412166.85</v>
@@ -6664,16 +6664,16 @@
         </is>
       </c>
       <c r="B26" s="18" t="n">
-        <v>-6702.63</v>
+        <v>-6717.63</v>
       </c>
       <c r="C26" s="18" t="n">
-        <v>-34646.27</v>
+        <v>-34723.78</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>60787.22</v>
+        <v>60923.2</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>75311.57000000001</v>
+        <v>76402.12</v>
       </c>
     </row>
     <row r="27">
@@ -6721,16 +6721,16 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>487478.42</v>
+        <v>488568.97</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>487478.42</v>
+        <v>488568.97</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>487478.42</v>
+        <v>488568.97</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>487478.42</v>
+        <v>488568.97</v>
       </c>
     </row>
     <row r="30">
@@ -6749,7 +6749,7 @@
         <v>14.25</v>
       </c>
       <c r="E30" s="21" t="n">
-        <v>18.27</v>
+        <v>18.54</v>
       </c>
     </row>
     <row r="31">
@@ -6818,7 +6818,7 @@
         </is>
       </c>
       <c r="B4" s="19" t="n">
-        <v>-44031.13</v>
+        <v>-44091.67</v>
       </c>
     </row>
     <row r="5">
@@ -6838,7 +6838,7 @@
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>-1252184.45</v>
+        <v>-1252060.75</v>
       </c>
     </row>
     <row r="7">
@@ -6848,7 +6848,7 @@
         </is>
       </c>
       <c r="B7" s="19" t="n">
-        <v>-804028.74</v>
+        <v>-803965.58</v>
       </c>
     </row>
     <row r="8">
@@ -6868,7 +6868,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>38690.57</v>
+        <v>38753.73</v>
       </c>
     </row>
     <row r="11">
@@ -7845,7 +7845,7 @@
         </is>
       </c>
       <c r="B96" s="4" t="n">
-        <v>1011218.51</v>
+        <v>1011202.12</v>
       </c>
     </row>
     <row r="97">
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="B97" s="13" t="n">
-        <v>1025407</v>
+        <v>1025356.19</v>
       </c>
     </row>
     <row r="98">
@@ -7865,7 +7865,7 @@
         </is>
       </c>
       <c r="B98" s="4" t="n">
-        <v>1026941.31</v>
+        <v>1026905.51</v>
       </c>
     </row>
     <row r="99">
@@ -7875,7 +7875,7 @@
         </is>
       </c>
       <c r="B99" s="13" t="n">
-        <v>1015258.85</v>
+        <v>1015273.3</v>
       </c>
     </row>
     <row r="100">
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="B100" s="4" t="n">
-        <v>1003003.03</v>
+        <v>1003025.8</v>
       </c>
     </row>
     <row r="101">
@@ -7895,7 +7895,7 @@
         </is>
       </c>
       <c r="B101" s="13" t="n">
-        <v>1013068.4</v>
+        <v>1013098.34</v>
       </c>
     </row>
     <row r="102">
@@ -7905,7 +7905,7 @@
         </is>
       </c>
       <c r="B102" s="4" t="n">
-        <v>1026667.89</v>
+        <v>1026718.34</v>
       </c>
     </row>
     <row r="103">
@@ -7915,7 +7915,7 @@
         </is>
       </c>
       <c r="B103" s="13" t="n">
-        <v>1053397.75</v>
+        <v>1053504.94</v>
       </c>
     </row>
     <row r="104">
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="B104" s="4" t="n">
-        <v>1050736.08</v>
+        <v>1050844.96</v>
       </c>
     </row>
     <row r="105">
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="B105" s="13" t="n">
-        <v>1049499.07</v>
+        <v>1049581.91</v>
       </c>
     </row>
     <row r="106">
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="B106" s="4" t="n">
-        <v>1049134.93</v>
+        <v>1049200.21</v>
       </c>
     </row>
     <row r="107">
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="B107" s="13" t="n">
-        <v>1042919.9</v>
+        <v>1042965.78</v>
       </c>
     </row>
     <row r="108">
@@ -7965,7 +7965,7 @@
         </is>
       </c>
       <c r="B108" s="4" t="n">
-        <v>1048685.92</v>
+        <v>1048734.43</v>
       </c>
     </row>
     <row r="109">
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="B109" s="13" t="n">
-        <v>1042773.4</v>
+        <v>1042822.5</v>
       </c>
     </row>
     <row r="110">
@@ -7985,7 +7985,7 @@
         </is>
       </c>
       <c r="B110" s="4" t="n">
-        <v>1044235.83</v>
+        <v>1044292.9</v>
       </c>
     </row>
     <row r="111">
@@ -7995,7 +7995,7 @@
         </is>
       </c>
       <c r="B111" s="13" t="n">
-        <v>1070354.14</v>
+        <v>1070408.83</v>
       </c>
     </row>
     <row r="112">
@@ -8005,7 +8005,7 @@
         </is>
       </c>
       <c r="B112" s="4" t="n">
-        <v>1061514.84</v>
+        <v>1061559.43</v>
       </c>
     </row>
     <row r="113">
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="B113" s="13" t="n">
-        <v>1074870.62</v>
+        <v>1074879.59</v>
       </c>
     </row>
     <row r="114">
@@ -8025,7 +8025,7 @@
         </is>
       </c>
       <c r="B114" s="4" t="n">
-        <v>1080512.52</v>
+        <v>1080503.54</v>
       </c>
     </row>
     <row r="115">
@@ -8035,7 +8035,7 @@
         </is>
       </c>
       <c r="B115" s="13" t="n">
-        <v>1086924.48</v>
+        <v>1086894.67</v>
       </c>
     </row>
     <row r="116">
@@ -8045,7 +8045,7 @@
         </is>
       </c>
       <c r="B116" s="4" t="n">
-        <v>1071780.32</v>
+        <v>1071796.37</v>
       </c>
     </row>
     <row r="117">
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="B117" s="13" t="n">
-        <v>1065526.09</v>
+        <v>1065522.69</v>
       </c>
     </row>
     <row r="118">
@@ -8065,7 +8065,7 @@
         </is>
       </c>
       <c r="B118" s="4" t="n">
-        <v>1080594.32</v>
+        <v>1080563.67</v>
       </c>
     </row>
     <row r="119">
@@ -8075,7 +8075,7 @@
         </is>
       </c>
       <c r="B119" s="13" t="n">
-        <v>1075591.99</v>
+        <v>1075540.76</v>
       </c>
     </row>
     <row r="120">
@@ -8085,7 +8085,7 @@
         </is>
       </c>
       <c r="B120" s="4" t="n">
-        <v>1071013.67</v>
+        <v>1070952.2</v>
       </c>
     </row>
     <row r="121">
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="B121" s="13" t="n">
-        <v>1073689.47</v>
+        <v>1073612.17</v>
       </c>
     </row>
     <row r="122">
@@ -8105,7 +8105,7 @@
         </is>
       </c>
       <c r="B122" s="4" t="n">
-        <v>1074236.64</v>
+        <v>1074160.56</v>
       </c>
     </row>
     <row r="123">
@@ -8115,7 +8115,7 @@
         </is>
       </c>
       <c r="B123" s="13" t="n">
-        <v>1084547.15</v>
+        <v>1084460.75</v>
       </c>
     </row>
     <row r="124">
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="B124" s="4" t="n">
-        <v>1085528.37</v>
+        <v>1085444.17</v>
       </c>
     </row>
     <row r="125">
@@ -8135,7 +8135,7 @@
         </is>
       </c>
       <c r="B125" s="13" t="n">
-        <v>1092616.33</v>
+        <v>1092531.84</v>
       </c>
     </row>
     <row r="126">
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="B126" s="4" t="n">
-        <v>1092781.06</v>
+        <v>1092690.79</v>
       </c>
     </row>
     <row r="127">
@@ -8155,7 +8155,7 @@
         </is>
       </c>
       <c r="B127" s="13" t="n">
-        <v>1053336.82</v>
+        <v>1053158.31</v>
       </c>
     </row>
     <row r="128">
@@ -8165,7 +8165,7 @@
         </is>
       </c>
       <c r="B128" s="4" t="n">
-        <v>1049687.33</v>
+        <v>1049512.64</v>
       </c>
     </row>
     <row r="129">
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="B129" s="13" t="n">
-        <v>1044100.12</v>
+        <v>1043936.06</v>
       </c>
     </row>
     <row r="130">
@@ -8185,7 +8185,7 @@
         </is>
       </c>
       <c r="B130" s="4" t="n">
-        <v>1032626.83</v>
+        <v>1032472.74</v>
       </c>
     </row>
     <row r="131">
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="B131" s="13" t="n">
-        <v>1039700.39</v>
+        <v>1039556.14</v>
       </c>
     </row>
     <row r="132">
@@ -8205,7 +8205,7 @@
         </is>
       </c>
       <c r="B132" s="4" t="n">
-        <v>1037551.62</v>
+        <v>1037415.03</v>
       </c>
     </row>
     <row r="133">
@@ -8215,7 +8215,7 @@
         </is>
       </c>
       <c r="B133" s="13" t="n">
-        <v>1019311.74</v>
+        <v>1019194.66</v>
       </c>
     </row>
     <row r="134">
@@ -8225,7 +8225,7 @@
         </is>
       </c>
       <c r="B134" s="4" t="n">
-        <v>1014163.76</v>
+        <v>1014068.88</v>
       </c>
     </row>
     <row r="135">
@@ -8235,7 +8235,7 @@
         </is>
       </c>
       <c r="B135" s="13" t="n">
-        <v>999293.04</v>
+        <v>999221.6800000001</v>
       </c>
     </row>
     <row r="136">
@@ -8245,7 +8245,7 @@
         </is>
       </c>
       <c r="B136" s="4" t="n">
-        <v>1011409.78</v>
+        <v>1011311.18</v>
       </c>
     </row>
     <row r="137">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="B137" s="13" t="n">
-        <v>1014540.8</v>
+        <v>1014433.88</v>
       </c>
     </row>
     <row r="138">
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="B138" s="4" t="n">
-        <v>1011881.11</v>
+        <v>1011774.92</v>
       </c>
     </row>
     <row r="139">
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="B139" s="13" t="n">
-        <v>998415.39</v>
+        <v>998320.26</v>
       </c>
     </row>
     <row r="140">
@@ -8285,7 +8285,7 @@
         </is>
       </c>
       <c r="B140" s="4" t="n">
-        <v>1014351.76</v>
+        <v>1014291.81</v>
       </c>
     </row>
     <row r="141">
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="B141" s="13" t="n">
-        <v>1023498.77</v>
+        <v>1023430.49</v>
       </c>
     </row>
     <row r="142">
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="B142" s="4" t="n">
-        <v>1023696.66</v>
+        <v>1023647.26</v>
       </c>
     </row>
     <row r="143">
@@ -8315,7 +8315,7 @@
         </is>
       </c>
       <c r="B143" s="13" t="n">
-        <v>996887.45</v>
+        <v>996791.04</v>
       </c>
     </row>
     <row r="144">
@@ -8325,7 +8325,7 @@
         </is>
       </c>
       <c r="B144" s="4" t="n">
-        <v>1016573.57</v>
+        <v>1016545.25</v>
       </c>
     </row>
     <row r="145">
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="B145" s="13" t="n">
-        <v>997861.24</v>
+        <v>997800.67</v>
       </c>
     </row>
     <row r="146">
@@ -8345,7 +8345,7 @@
         </is>
       </c>
       <c r="B146" s="4" t="n">
-        <v>991493.7</v>
+        <v>991400.37</v>
       </c>
     </row>
     <row r="147">
@@ -8355,7 +8355,7 @@
         </is>
       </c>
       <c r="B147" s="13" t="n">
-        <v>989347.35</v>
+        <v>989233.28</v>
       </c>
     </row>
     <row r="148">
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="B148" s="4" t="n">
-        <v>1004898.62</v>
+        <v>1004807.41</v>
       </c>
     </row>
     <row r="149">
@@ -8375,7 +8375,7 @@
         </is>
       </c>
       <c r="B149" s="13" t="n">
-        <v>1099657.36</v>
+        <v>1099781.06</v>
       </c>
     </row>
     <row r="150">
@@ -8385,7 +8385,7 @@
         </is>
       </c>
       <c r="B150" s="4" t="n">
-        <v>1108417.28</v>
+        <v>1108558.05</v>
       </c>
     </row>
     <row r="151">
@@ -8395,7 +8395,7 @@
         </is>
       </c>
       <c r="B151" s="13" t="n">
-        <v>1111711.73</v>
+        <v>1111869.67</v>
       </c>
     </row>
     <row r="152">
@@ -8405,7 +8405,7 @@
         </is>
       </c>
       <c r="B152" s="4" t="n">
-        <v>1007255.64</v>
+        <v>1007201.77</v>
       </c>
     </row>
     <row r="153">
@@ -8415,7 +8415,7 @@
         </is>
       </c>
       <c r="B153" s="13" t="n">
-        <v>1063725.16</v>
+        <v>1063800.8</v>
       </c>
     </row>
     <row r="154">
@@ -8425,7 +8425,7 @@
         </is>
       </c>
       <c r="B154" s="4" t="n">
-        <v>1055626.23</v>
+        <v>1055689.39</v>
       </c>
     </row>
   </sheetData>
@@ -8530,7 +8530,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1055626.23</v>
+        <v>1055689.39</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>1006991.94</v>
@@ -8551,10 +8551,10 @@
         <v>0.483</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>142.49</v>
+        <v>142.48</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>71.25</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="K4" s="23" t="n">
         <v>9</v>
@@ -8567,7 +8567,7 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>568147.8100000001</v>
+        <v>567120.42</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>97067.52</v>
@@ -8588,10 +8588,10 @@
         <v>-0.001</v>
       </c>
       <c r="I5" s="24" t="n">
-        <v>34.26</v>
+        <v>34.32</v>
       </c>
       <c r="J5" s="24" t="n">
-        <v>17.13</v>
+        <v>17.16</v>
       </c>
       <c r="K5" s="25" t="n">
         <v>1</v>
@@ -8604,7 +8604,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>487478.42</v>
+        <v>488568.97</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>909924.42</v>
@@ -8619,16 +8619,16 @@
         <v>510295.48</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>2.686</v>
+        <v>2.68</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>1.047</v>
+        <v>1.044</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>268.64</v>
+        <v>268.04</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>134.32</v>
+        <v>134.02</v>
       </c>
       <c r="K6" s="23" t="n">
         <v>8</v>
@@ -8718,7 +8718,7 @@
         <v>273577.2</v>
       </c>
       <c r="D6" s="27" t="n">
-        <v>25.92</v>
+        <v>25.91</v>
       </c>
       <c r="E6" s="27" t="n">
         <v>18.19</v>
@@ -8850,7 +8850,7 @@
         <v>97067.52</v>
       </c>
       <c r="D12" s="27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="E12" s="27" t="n">
         <v>6.45</v>

--- a/trading_signals/risk_management/risk_workbook_20260610_031024.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260610_031024.xlsx
@@ -731,7 +731,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-09  ·  Generated 2026-06-24T18:50:51  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-09  ·  Generated 2026-06-25T01:49:24  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>
